--- a/public/templates/cha-jewels-product-upload-template.xlsx
+++ b/public/templates/cha-jewels-product-upload-template.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Upload" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Lists" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Hub field map" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Reference" sheetId="5" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -1177,7 +1178,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AH204"/>
+  <dimension ref="A1:AJ204"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="18"/>
@@ -1295,6 +1296,16 @@
           <t xml:space="preserve">hub_brand</t>
         </is>
       </c>
+      <c r="AI1" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collection_slugs</t>
+        </is>
+      </c>
+      <c r="AJ1" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">category_slugs</t>
+        </is>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -1403,6 +1414,16 @@
           <t xml:space="preserve">optional</t>
         </is>
       </c>
+      <c r="AI2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">optional</t>
+        </is>
+      </c>
+      <c r="AJ2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">optional</t>
+        </is>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
@@ -1511,6 +1532,16 @@
           <t xml:space="preserve">Brand name, e.g. Tiffany &amp; Co. Required when hub_origin is Branded; shown on the site only then. Name only — never a logo.</t>
         </is>
       </c>
+      <c r="AI3" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Extra jewelry types for this piece, by slug, separated with | (e.g. necklaces|pendants). hub_jewelry_type stays the main type. Slugs are listed on the Reference sheet and in the upload dialog. Blank = keep the piece’s existing types.</t>
+        </is>
+      </c>
+      <c r="AJ3" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website categories for this piece, by slug, separated with | (e.g. preloved|gifts). Slugs are listed on the Reference sheet and in the upload dialog. Blank = keep the piece’s existing categories; the import never removes categories unless you choose Replace.</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
@@ -1617,6 +1648,16 @@
       <c r="AH4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Hub: Edit product › brand</t>
+        </is>
+      </c>
+      <c r="AI4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hub: Edit product › Jewelry types</t>
+        </is>
+      </c>
+      <c r="AJ4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hub: Edit product › Categories</t>
         </is>
       </c>
     </row>
@@ -12042,4 +12083,98 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="110" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collection_slug</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">category_slug</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">anklets</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collection_slug: the jewelry types the Hub shipped with. The live list is Hub › Website Catalog › Jewelry types.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bracelets</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">category_slug: categories are managed in Hub › Website Catalog › Categories; the upload dialog lists the live slugs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earrings</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Separate several slugs with | in collection_slugs / category_slugs on the Upload sheet. Unknown slugs stop the row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">necklaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pendants</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rings</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sets</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/public/templates/cha-jewels-product-upload-template.xlsx
+++ b/public/templates/cha-jewels-product-upload-template.xlsx
@@ -339,7 +339,7 @@
     <t xml:space="preserve">Hub: Edit product › status</t>
   </si>
   <si>
-    <t xml:space="preserve">Hub: Edit product › design</t>
+    <t xml:space="preserve">Name part only — not imported</t>
   </si>
   <si>
     <t xml:space="preserve">R3341</t>
@@ -11572,7 +11572,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -11722,6 +11722,13 @@
     <row r="14">
       <c r="B14" t="s">
         <v>132</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The import dialog shows the live list; this sheet is a snapshot</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -11740,7 +11747,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
@@ -12071,6 +12078,60 @@
       <c r="E18" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Tiffany &amp; Co.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">collection_slugs</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">optional</t>
+        </is>
+      </c>
+      <c r="C19" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jewelry types</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Extra jewelry types for this piece, by slug, separated with |. hub_jewelry_type stays the main type. Blank = keep the piece's existing types.</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">necklaces|pendants</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">category_slugs</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">optional</t>
+        </is>
+      </c>
+      <c r="C20" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Categories</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Website categories for this piece, by slug, separated with |. Blank = keep the piece's existing categories; only Replace removes them.</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">preloved|gifts</t>
         </is>
       </c>
     </row>
@@ -12153,6 +12214,11 @@
           <t xml:space="preserve">necklaces</t>
         </is>
       </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The import dialog shows the live list; this sheet is a snapshot</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">

--- a/public/templates/cha-jewels-product-upload-template.xlsx
+++ b/public/templates/cha-jewels-product-upload-template.xlsx
@@ -1178,7 +1178,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AJ204"/>
+  <dimension ref="A1:AK204"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="18"/>
@@ -1187,6 +1187,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="13" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="25" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="20"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1306,6 +1307,11 @@
           <t xml:space="preserve">category_slugs</t>
         </is>
       </c>
+      <c r="AK1" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hub_sale_price</t>
+        </is>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
@@ -1424,6 +1430,11 @@
           <t xml:space="preserve">optional</t>
         </is>
       </c>
+      <c r="AK2" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">optional</t>
+        </is>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="79.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
@@ -1542,6 +1553,11 @@
           <t xml:space="preserve">Website categories for this piece, by slug, separated with | (e.g. preloved|gifts). Slugs are listed on the Reference sheet and in the upload dialog. Blank = keep the piece’s existing categories; the import never removes categories unless you choose Replace.</t>
         </is>
       </c>
+      <c r="AK3" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Optional sale price in whole yen, below price. Blank = keep the piece's existing sale (none on a new piece); remove a sale in Edit product. The website charges it and shows price struck through beside it.</t>
+        </is>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
@@ -1658,6 +1674,11 @@
       <c r="AJ4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Hub: Edit product › Categories</t>
+        </is>
+      </c>
+      <c r="AK4" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hub: Edit product › Sale price (JPY)</t>
         </is>
       </c>
     </row>
@@ -11747,7 +11768,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
@@ -12132,6 +12153,33 @@
       <c r="E20" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">preloved|gifts</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hub_sale_price</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">optional</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sale price (JPY)</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Integer yen, below price. Blank = keep the existing sale (remove one in Edit product). The website charges it everywhere and shows price struck through.</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">550000</t>
         </is>
       </c>
     </row>
